--- a/data/trans_orig/IP07C12-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07C12-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse que sus padres hayan tenido suficiente tiempo par él/ella en 2007 (tasa de respuesta: 89,59%)</t>
+          <t>Menores según la frecuencia de sentir que sus padres han tenido suficiente tiempo para él/ella en 2007 (tasa de respuesta: 89,59%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16016</t>
+          <t>16030</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25817</t>
+          <t>26106</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13377</t>
+          <t>13222</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22932</t>
+          <t>23150</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32209</t>
+          <t>31758</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45520</t>
+          <t>45846</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>61,09%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7092</t>
+          <t>6860</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16454</t>
+          <t>16439</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8006</t>
+          <t>8221</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17296</t>
+          <t>17365</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17722</t>
+          <t>17599</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30674</t>
+          <t>30408</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,52%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9027</t>
+          <t>9324</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8537</t>
+          <t>9063</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5752</t>
+          <t>5595</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14945</t>
+          <t>15572</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>726</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6426</t>
+          <t>6566</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>724</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>6355</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8743</t>
+          <t>8795</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16773</t>
+          <t>16780</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11491</t>
+          <t>11366</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20276</t>
+          <t>20315</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23098</t>
+          <t>22725</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34781</t>
+          <t>34175</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>63,25%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13068</t>
+          <t>13051</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5886</t>
+          <t>5652</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13988</t>
+          <t>13713</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12886</t>
+          <t>13121</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>24249</t>
+          <t>24323</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>45,02%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>638</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5912</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1857</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7916</t>
+          <t>7855</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11234</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>19,37%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>2612</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9945</t>
+          <t>10372</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18661</t>
+          <t>18691</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23043</t>
+          <t>24085</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35099</t>
+          <t>35021</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36347</t>
+          <t>36671</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51079</t>
+          <t>51257</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,98%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>5969</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14683</t>
+          <t>14302</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10759</t>
+          <t>10989</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21613</t>
+          <t>21684</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18880</t>
+          <t>18758</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33165</t>
+          <t>32642</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>40,74%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7560</t>
+          <t>6841</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>2790</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10749</t>
+          <t>10076</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5355</t>
+          <t>5202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14489</t>
+          <t>14319</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>3901</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>33457</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47479</t>
+          <t>47995</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>56,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38095</t>
+          <t>38655</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51655</t>
+          <t>52568</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>75801</t>
+          <t>75049</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>97416</t>
+          <t>96400</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,06%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26401</t>
+          <t>25442</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>40263</t>
+          <t>40114</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>16694</t>
+          <t>16957</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>29563</t>
+          <t>29997</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>46218</t>
+          <t>46168</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>67581</t>
+          <t>65922</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>39,7%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7649</t>
+          <t>7363</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18006</t>
+          <t>17028</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7382</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17721</t>
+          <t>17658</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>17222</t>
+          <t>17728</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>31141</t>
+          <t>31967</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>19,25%</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3589</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>19088</t>
+          <t>19137</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>30301</t>
+          <t>30067</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>26636</t>
+          <t>26161</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>38973</t>
+          <t>39389</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>47624</t>
+          <t>48377</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>65015</t>
+          <t>65610</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>59,33%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9387</t>
+          <t>9894</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>19875</t>
+          <t>19649</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>13174</t>
+          <t>12567</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>25136</t>
+          <t>24611</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>25868</t>
+          <t>25516</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>41287</t>
+          <t>41239</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,29%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4429</t>
+          <t>4578</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12857</t>
+          <t>13177</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6719</t>
+          <t>6930</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>16439</t>
+          <t>16661</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>13212</t>
+          <t>12980</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>26117</t>
+          <t>26363</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,84%</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3718</t>
+          <t>3681</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4248</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3240</t>
+          <t>2625</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>3465</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>15280</t>
+          <t>15103</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>24686</t>
+          <t>25032</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>13309</t>
+          <t>12727</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>21923</t>
+          <t>21986</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>30375</t>
+          <t>31767</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>44194</t>
+          <t>44378</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>63,66%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>9841</t>
+          <t>9541</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>19205</t>
+          <t>19123</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>5725</t>
+          <t>5361</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>14273</t>
+          <t>14263</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>17762</t>
+          <t>18372</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>30515</t>
+          <t>30498</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>43,75%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>603</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4530</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1469</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7982</t>
+          <t>8297</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2794</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>10656</t>
+          <t>10345</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>4276</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>3395</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>3666</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>120104</t>
+          <t>119280</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>146291</t>
+          <t>146296</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>144556</t>
+          <t>143996</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>172242</t>
+          <t>172127</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>272060</t>
+          <t>273015</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>310494</t>
+          <t>309394</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>55,69%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>79962</t>
+          <t>79948</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>104993</t>
+          <t>104098</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>76367</t>
+          <t>77283</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>102312</t>
+          <t>102392</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>164247</t>
+          <t>163458</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>198128</t>
+          <t>198491</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,73%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>24139</t>
+          <t>24343</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>42124</t>
+          <t>41397</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>33628</t>
+          <t>33662</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>52303</t>
+          <t>53099</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>62834</t>
+          <t>61398</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>88256</t>
+          <t>87128</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>2777</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>10975</t>
+          <t>11387</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>3767</t>
+          <t>3795</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>12534</t>
+          <t>12973</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>4728</t>
+          <t>4587</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>4705</t>
+          <t>4109</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse que sus padres hayan tenido suficiente tiempo par él/ella en 2012 (tasa de respuesta: 95,62%)</t>
+          <t>Menores según la frecuencia de sentir que sus padres han tenido suficiente tiempo para él/ella en 2012 (tasa de respuesta: 95,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14782</t>
+          <t>14941</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25022</t>
+          <t>24764</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10603</t>
+          <t>10669</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19983</t>
+          <t>19906</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28434</t>
+          <t>27915</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42251</t>
+          <t>41955</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>58,98%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13736</t>
+          <t>13141</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>9989</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19574</t>
+          <t>19174</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16557</t>
+          <t>17172</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29531</t>
+          <t>29551</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,55%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4807</t>
+          <t>4882</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13332</t>
+          <t>13758</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2069</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8770</t>
+          <t>8757</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8658</t>
+          <t>8452</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19838</t>
+          <t>19509</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,43%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11826</t>
+          <t>11852</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21032</t>
+          <t>21257</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17571</t>
+          <t>17869</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27022</t>
+          <t>26867</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31600</t>
+          <t>31358</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45058</t>
+          <t>45204</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>66,76%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t>9123</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18721</t>
+          <t>18649</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6053</t>
+          <t>6115</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>14937</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17940</t>
+          <t>18461</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>31031</t>
+          <t>31418</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>46,4%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>702</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>5962</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>680</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5737</t>
+          <t>5837</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>2242</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9487</t>
+          <t>9026</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15693</t>
+          <t>15787</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26315</t>
+          <t>26502</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9615</t>
+          <t>9915</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18103</t>
+          <t>18415</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27844</t>
+          <t>27837</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41353</t>
+          <t>41985</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>56,45%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12961</t>
+          <t>13081</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23146</t>
+          <t>23718</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9861</t>
+          <t>9857</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18888</t>
+          <t>18518</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25666</t>
+          <t>26023</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39101</t>
+          <t>39985</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>53,76%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1425</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8144</t>
+          <t>8281</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7291</t>
+          <t>7251</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3651</t>
+          <t>3808</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12287</t>
+          <t>12013</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,15%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40353</t>
+          <t>40631</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55604</t>
+          <t>55927</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47672</t>
+          <t>47232</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62998</t>
+          <t>63232</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>92294</t>
+          <t>92808</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>113648</t>
+          <t>113829</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>62,75%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21219</t>
+          <t>20906</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>35358</t>
+          <t>35330</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>25276</t>
+          <t>24938</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>40495</t>
+          <t>40315</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>48963</t>
+          <t>49980</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>69377</t>
+          <t>70609</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,93%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11150</t>
+          <t>11285</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5448</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14891</t>
+          <t>14392</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9700</t>
+          <t>10286</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>22073</t>
+          <t>22390</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6023</t>
+          <t>5412</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4648</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>827</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7638</t>
+          <t>7076</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>39428</t>
+          <t>39544</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>53308</t>
+          <t>53014</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>34767</t>
+          <t>34758</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>48794</t>
+          <t>48734</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>76709</t>
+          <t>77617</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>97246</t>
+          <t>97395</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>66,39%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11070</t>
+          <t>11273</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>22694</t>
+          <t>22215</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>18007</t>
+          <t>17998</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>31238</t>
+          <t>31303</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>32507</t>
+          <t>32728</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>50651</t>
+          <t>50256</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,26%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6237</t>
+          <t>6046</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>16894</t>
+          <t>16382</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8431</t>
+          <t>8844</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>9950</t>
+          <t>9701</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>22442</t>
+          <t>22384</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,26%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>637</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>6180</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>3157</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>817</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7191</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>8452</t>
+          <t>8481</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>16226</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>16660</t>
+          <t>17164</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>26536</t>
+          <t>26857</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>27598</t>
+          <t>27500</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>39901</t>
+          <t>39989</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,96%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4374</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>12250</t>
+          <t>12025</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>5383</t>
+          <t>5458</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>14401</t>
+          <t>14377</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>11887</t>
+          <t>11889</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>23058</t>
+          <t>23391</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,75%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>7057</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>771</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7274</t>
+          <t>7329</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3290</t>
+          <t>2822</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>11599</t>
+          <t>11711</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,9%</t>
         </is>
       </c>
     </row>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3728</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>148633</t>
+          <t>150600</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>177425</t>
+          <t>178554</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>156250</t>
+          <t>155559</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>182652</t>
+          <t>185276</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>313541</t>
+          <t>311636</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>353823</t>
+          <t>353097</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>58,84%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>80018</t>
+          <t>78889</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>106900</t>
+          <t>105866</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>93146</t>
+          <t>90164</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>118783</t>
+          <t>119001</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>177632</t>
+          <t>178609</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>215617</t>
+          <t>216687</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>36,11%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>26250</t>
+          <t>25591</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>44581</t>
+          <t>45771</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>20641</t>
+          <t>20368</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>37162</t>
+          <t>35620</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>50220</t>
+          <t>50344</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>75200</t>
+          <t>74372</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1465</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>9130</t>
+          <t>8894</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>626</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>6721</t>
+          <t>6649</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>3383</t>
+          <t>3382</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>13134</t>
+          <t>12261</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse que sus padres hayan tenido suficiente tiempo par él/ella en 2016 (tasa de respuesta: 95,18%)</t>
+          <t>Menores según la frecuencia de sentir que sus padres han tenido suficiente tiempo para él/ella en 2016 (tasa de respuesta: 95,18%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17545</t>
+          <t>17625</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26319</t>
+          <t>26456</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14827</t>
+          <t>14661</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25129</t>
+          <t>24737</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35274</t>
+          <t>36208</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49089</t>
+          <t>49020</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>69,98%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2484</t>
+          <t>2388</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9127</t>
+          <t>8903</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>9527</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19369</t>
+          <t>19640</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13526</t>
+          <t>13049</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25724</t>
+          <t>25135</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>35,88%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7947</t>
+          <t>7482</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7527</t>
+          <t>6898</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>3793</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11997</t>
+          <t>12223</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -11092,7 +11092,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3781</t>
+          <t>4520</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11107,7 +11107,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11162,7 +11162,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3754</t>
+          <t>4352</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -11205,7 +11205,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3616</t>
+          <t>3365</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4428</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15214</t>
+          <t>15460</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27181</t>
+          <t>26904</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22143</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34426</t>
+          <t>33966</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41243</t>
+          <t>41585</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57904</t>
+          <t>58343</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>61,01%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13491</t>
+          <t>13041</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24641</t>
+          <t>24622</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18140</t>
+          <t>18176</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23513</t>
+          <t>23608</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>39420</t>
+          <t>39172</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>40,96%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3460</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12679</t>
+          <t>12097</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2501</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10305</t>
+          <t>10006</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7695</t>
+          <t>7925</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18929</t>
+          <t>19291</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -11774,7 +11774,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4629</t>
+          <t>4573</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>554</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6795</t>
+          <t>6960</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10306</t>
+          <t>10447</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19427</t>
+          <t>18953</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15040</t>
+          <t>15385</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25315</t>
+          <t>25471</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28995</t>
+          <t>28210</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42531</t>
+          <t>42231</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>62,61%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5710</t>
+          <t>5518</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14033</t>
+          <t>13967</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11604</t>
+          <t>11029</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21637</t>
+          <t>21553</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19655</t>
+          <t>19622</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32103</t>
+          <t>33170</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>49,17%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>730</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6822</t>
+          <t>6791</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>761</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7485</t>
+          <t>6964</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11556</t>
+          <t>12120</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>50062</t>
+          <t>50095</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67951</t>
+          <t>66999</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41584</t>
+          <t>42058</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>58176</t>
+          <t>58609</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>97958</t>
+          <t>97446</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>121282</t>
+          <t>121732</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>58,29%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>25453</t>
+          <t>25842</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>42993</t>
+          <t>42126</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>29552</t>
+          <t>28203</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>45745</t>
+          <t>45306</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>58736</t>
+          <t>59449</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>82169</t>
+          <t>81692</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,11%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10469</t>
+          <t>10574</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23276</t>
+          <t>22875</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5929</t>
+          <t>6235</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>16625</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>18661</t>
+          <t>18485</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>34573</t>
+          <t>34854</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,69%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>650</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5773</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>696</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6092</t>
+          <t>6256</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29912</t>
+          <t>30162</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>43991</t>
+          <t>44049</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>30797</t>
+          <t>30182</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>44615</t>
+          <t>43980</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>64005</t>
+          <t>65679</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>84904</t>
+          <t>85429</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,55%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>26307</t>
+          <t>25871</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>39741</t>
+          <t>39358</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>19683</t>
+          <t>20072</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>32912</t>
+          <t>33837</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>48546</t>
+          <t>49114</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>69413</t>
+          <t>69177</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>48,22%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>1583</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>9245</t>
+          <t>8911</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8006</t>
+          <t>7722</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4296</t>
+          <t>4708</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>13606</t>
+          <t>14266</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -13855,7 +13855,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4464</t>
+          <t>4805</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>10598</t>
+          <t>10704</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>20538</t>
+          <t>19942</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>17032</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>27091</t>
+          <t>27582</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>30529</t>
+          <t>30631</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>44505</t>
+          <t>46014</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>65,25%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6731</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>16012</t>
+          <t>16542</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>6937</t>
+          <t>7006</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>16546</t>
+          <t>16560</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>16377</t>
+          <t>16140</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>29972</t>
+          <t>30256</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,91%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6954</t>
+          <t>7051</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7460</t>
+          <t>7633</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3497</t>
+          <t>3344</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>11327</t>
+          <t>11804</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,74%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>573</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5598</t>
+          <t>5646</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>564</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5734</t>
+          <t>6101</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -14615,7 +14615,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4373</t>
+          <t>3870</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4164</t>
+          <t>4487</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>156413</t>
+          <t>156159</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>186302</t>
+          <t>185765</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>165153</t>
+          <t>162929</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>193174</t>
+          <t>194061</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>330573</t>
+          <t>326326</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>372665</t>
+          <t>370144</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>56,43%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>96009</t>
+          <t>96155</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>123415</t>
+          <t>125389</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>103558</t>
+          <t>102328</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>130921</t>
+          <t>133014</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>207755</t>
+          <t>208261</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>247116</t>
+          <t>248297</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,85%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>28219</t>
+          <t>28258</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>47335</t>
+          <t>47577</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>22223</t>
+          <t>21941</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>38901</t>
+          <t>38838</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>54350</t>
+          <t>55672</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>80300</t>
+          <t>80513</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>11197</t>
+          <t>10860</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>717</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>7522</t>
+          <t>7360</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15234,7 +15234,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>15778</t>
+          <t>15765</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -15292,82 +15292,82 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
+          <t>569</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>5147</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>1925</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
           <t>567</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>4951</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>1925</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>572</t>
-        </is>
-      </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5312</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15382,7 +15382,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
